--- a/thaco/Pay-slip.xlsx
+++ b/thaco/Pay-slip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thaco-my.sharepoint.com/personal/nguyentamquang_thaco_com_vn/Documents/1. CNTT VP HCM/01. QUAN TRI CNTT/0. DU AN CNTT/02. DU AN NHAN SU/HO SO DU AN/Mẫu bảng công - bảng lương/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{168401FA-E9DE-47D8-BAB2-7510FA910D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA868F9-C65D-9640-BB30-74B3B619CA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32CB156E-D7EF-48E2-ABB5-EC622FB03A24}"/>
+    <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{32CB156E-D7EF-48E2-ABB5-EC622FB03A24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -190,7 +189,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -390,6 +389,36 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -410,36 +439,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -776,328 +775,335 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD30E6F-4E63-4E27-B206-A3E07477E768}">
   <dimension ref="D4:F47"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.75" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="14" t="s">
+    <row r="4" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="4:6" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-    </row>
-    <row r="6" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="25"/>
+      <c r="F5" s="26"/>
+    </row>
+    <row r="6" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="27">
         <v>25050570</v>
       </c>
-      <c r="F6" s="18"/>
-    </row>
-    <row r="7" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="20"/>
-    </row>
-    <row r="8" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="14">
         <v>26</v>
       </c>
-      <c r="F8" s="22"/>
-    </row>
-    <row r="9" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
-    </row>
-    <row r="10" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="22"/>
+      <c r="F9" s="23"/>
+    </row>
+    <row r="10" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
-    </row>
-    <row r="11" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-    </row>
-    <row r="12" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="16"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="22"/>
-    </row>
-    <row r="13" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="14"/>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="13" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
-    </row>
-    <row r="14" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="14"/>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
-    </row>
-    <row r="15" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="26"/>
-    </row>
-    <row r="16" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+    </row>
+    <row r="16" spans="4:6" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24"/>
-    </row>
-    <row r="17" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="22"/>
+      <c r="F16" s="23"/>
+    </row>
+    <row r="17" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D18" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D29" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D31" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D33" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D36" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="23"/>
-      <c r="F36" s="24"/>
-    </row>
-    <row r="37" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="22"/>
+      <c r="F36" s="23"/>
+    </row>
+    <row r="37" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D37" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="26"/>
-    </row>
-    <row r="38" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E37" s="16"/>
+      <c r="F37" s="17"/>
+    </row>
+    <row r="38" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="22"/>
-    </row>
-    <row r="39" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D39" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="22"/>
-    </row>
-    <row r="40" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="14"/>
+      <c r="F39" s="15"/>
+    </row>
+    <row r="40" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D40" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="22"/>
-    </row>
-    <row r="41" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E40" s="14"/>
+      <c r="F40" s="15"/>
+    </row>
+    <row r="41" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D41" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E41" s="21"/>
-      <c r="F41" s="22"/>
-    </row>
-    <row r="42" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="14"/>
+      <c r="F41" s="15"/>
+    </row>
+    <row r="42" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D42" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E42" s="21"/>
-      <c r="F42" s="22"/>
-    </row>
-    <row r="43" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="14"/>
+      <c r="F42" s="15"/>
+    </row>
+    <row r="43" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E43" s="25"/>
-      <c r="F43" s="26"/>
-    </row>
-    <row r="44" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E43" s="16"/>
+      <c r="F43" s="17"/>
+    </row>
+    <row r="44" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D44" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E44" s="21"/>
-      <c r="F44" s="22"/>
-    </row>
-    <row r="45" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E44" s="14"/>
+      <c r="F44" s="15"/>
+    </row>
+    <row r="45" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D45" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E45" s="27"/>
-      <c r="F45" s="28"/>
-    </row>
-    <row r="46" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E45" s="18"/>
+      <c r="F45" s="19"/>
+    </row>
+    <row r="46" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D46" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E46" s="29"/>
-      <c r="F46" s="30"/>
-    </row>
-    <row r="47" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="20"/>
+      <c r="F46" s="21"/>
+    </row>
+    <row r="47" spans="4:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D47" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E47" s="29"/>
-      <c r="F47" s="30"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="E37:F37"/>
@@ -1105,18 +1111,11 @@
     <mergeCell ref="E39:F39"/>
     <mergeCell ref="E40:F40"/>
     <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
